--- a/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
+++ b/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12990" windowHeight="5865"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12990" windowHeight="5865" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="CONTAS A PAGAR" sheetId="5" r:id="rId1"/>
@@ -17,7 +17,6 @@
     <sheet name="ANALISES" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="63">
   <si>
     <t>CONTAS A RECEBER</t>
   </si>
@@ -63,13 +62,169 @@
   </si>
   <si>
     <t>CLIENTE</t>
+  </si>
+  <si>
+    <t>Gráfica Rápida</t>
+  </si>
+  <si>
+    <t>Conta de Luz</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>Cartão de Crédito</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>Aluguel Imóveis</t>
+  </si>
+  <si>
+    <t>Hospedagem de Site</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Consultoria XPTO</t>
+  </si>
+  <si>
+    <t>Material de Escritório</t>
+  </si>
+  <si>
+    <t>Boleto</t>
+  </si>
+  <si>
+    <t>Vendas</t>
+  </si>
+  <si>
+    <t>Limpeza &amp; Cia</t>
+  </si>
+  <si>
+    <t>Assinatura de Software</t>
+  </si>
+  <si>
+    <t>Energia S.A.</t>
+  </si>
+  <si>
+    <t>Seguro Predial</t>
+  </si>
+  <si>
+    <t>Operacional</t>
+  </si>
+  <si>
+    <t>AWS Amazon</t>
+  </si>
+  <si>
+    <t>Manutenção de Ar-condicionado</t>
+  </si>
+  <si>
+    <t>Campanha de Marketing</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>Pix</t>
+  </si>
+  <si>
+    <t>Papelaria Silva</t>
+  </si>
+  <si>
+    <t>Serviços de Consultoria</t>
+  </si>
+  <si>
+    <t>Transferência Bancária</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Insumos de Produção</t>
+  </si>
+  <si>
+    <t>Financeiro</t>
+  </si>
+  <si>
+    <t>Seguros Porto</t>
+  </si>
+  <si>
+    <t>Limpeza Mensal</t>
+  </si>
+  <si>
+    <t>Internet Fibra</t>
+  </si>
+  <si>
+    <t>Varejo Global</t>
+  </si>
+  <si>
+    <t>Suporte Premium</t>
+  </si>
+  <si>
+    <t>Construtora Alfa</t>
+  </si>
+  <si>
+    <t>Projeto de Software</t>
+  </si>
+  <si>
+    <t>Supermercado Real</t>
+  </si>
+  <si>
+    <t>Venda de Equipamento</t>
+  </si>
+  <si>
+    <t>João Silva</t>
+  </si>
+  <si>
+    <t>Manutenção de Sistema</t>
+  </si>
+  <si>
+    <t>Academia Fit</t>
+  </si>
+  <si>
+    <t>Venda de Licença</t>
+  </si>
+  <si>
+    <t>Escola Aprender</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Site</t>
+  </si>
+  <si>
+    <t>Hospital Vida</t>
+  </si>
+  <si>
+    <t>Consultoria Técnica</t>
+  </si>
+  <si>
+    <t>Restaurante Sabor</t>
+  </si>
+  <si>
+    <t>Tech Solutions Ltda</t>
+  </si>
+  <si>
+    <t>Prestação de Serviço Mensal</t>
+  </si>
+  <si>
+    <t>Maria Oliveira</t>
+  </si>
+  <si>
+    <t>Curso de Treinamento</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -86,6 +241,21 @@
     </font>
     <font>
       <sz val="36"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -120,33 +290,446 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right style="thin">
+          <color theme="9"/>
+        </right>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -154,89 +737,16 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9"/>
+        </left>
+        <right style="thin">
+          <color theme="9"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -269,36 +779,24 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -311,6 +809,41 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C6500"/>
       </font>
@@ -322,13 +855,45 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -347,27 +912,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>262371</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>807893</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>64943</xdr:rowOff>
+      <xdr:rowOff>45893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1817544</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>232930</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>569768</xdr:rowOff>
+      <xdr:rowOff>550718</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Retângulo Arredondado 1">
+        <xdr:cNvPr id="4" name="Retângulo Arredondado 3">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3570144" y="64943"/>
+          <a:off x="7672821" y="45893"/>
           <a:ext cx="1565564" cy="504825"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -376,7 +941,9 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1"/>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -414,14 +981,8 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>CONTAS A PAGAR</a:t>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>ANÁLISES</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -431,27 +992,27 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>395722</xdr:colOff>
+      <xdr:colOff>443968</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>49357</xdr:rowOff>
+      <xdr:rowOff>51148</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>288349</xdr:colOff>
+      <xdr:colOff>336595</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>554182</xdr:rowOff>
+      <xdr:rowOff>555973</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Retângulo Arredondado 2">
+        <xdr:cNvPr id="15" name="Retângulo Arredondado 14">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5587713" y="49357"/>
-          <a:ext cx="1562100" cy="504825"/>
+          <a:off x="5607175" y="51148"/>
+          <a:ext cx="1548006" cy="504825"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -509,28 +1070,28 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>807893</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>301785</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45893</xdr:rowOff>
+      <xdr:rowOff>38667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>232930</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1856958</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>550718</xdr:rowOff>
+      <xdr:rowOff>543492</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Retângulo Arredondado 3">
+        <xdr:cNvPr id="16" name="Retângulo Arredondado 15">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7672821" y="45893"/>
-          <a:ext cx="1565564" cy="504825"/>
+          <a:off x="3586268" y="38667"/>
+          <a:ext cx="1555173" cy="504825"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -538,9 +1099,7 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg1"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -578,8 +1137,14 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="pt-BR" sz="1600"/>
-            <a:t>ANÁLISES</a:t>
+            <a:rPr lang="pt-BR" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>CONTAS A PAGAR</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1090,48 +1655,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B4:I5" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="B4:I5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B4:I31" headerRowDxfId="37" dataDxfId="36">
+  <autoFilter ref="B4:I31"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="20">
+    <tableColumn id="1" name="DATA DE VENCIMENTO" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="17">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="FORNECEDOR" dataDxfId="19"/>
-    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="18"/>
-    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="17"/>
-    <tableColumn id="5" name="STATUS" dataDxfId="16">
+    <tableColumn id="2" name="FORNECEDOR" dataDxfId="34" totalsRowDxfId="18"/>
+    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="30" totalsRowDxfId="19"/>
+    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="28" totalsRowDxfId="20" dataCellStyle="Moeda"/>
+    <tableColumn id="5" name="STATUS" dataDxfId="29" totalsRowDxfId="21">
       <calculatedColumnFormula>IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="15">
+    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="33" totalsRowDxfId="22">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="14"/>
-    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="13"/>
+    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="32" totalsRowDxfId="23"/>
+    <tableColumn id="8" name="CENTRO DE CUSTO" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela13" displayName="Tabela13" ref="B3:I4" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="B3:I4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="B3:I28" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
+  <autoFilter ref="B3:I28"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="7">
+    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="8"/>
+    <tableColumn id="2" name="CLIENTE" dataDxfId="7"/>
+    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="6"/>
+    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="5"/>
+    <tableColumn id="5" name="STATUS" dataDxfId="4"/>
+    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="3">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="CLIENTE" dataDxfId="6"/>
-    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="5"/>
-    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="4"/>
-    <tableColumn id="5" name="STATUS" dataDxfId="3">
-      <calculatedColumnFormula>IF(G4&lt;&gt;"","PAGO",IF(B4&lt;TODAY(),"ATRASADO","PENDENTE"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="2">
-      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="1"/>
-    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="0"/>
+    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="2"/>
+    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="1"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1398,13 +1959,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.42578125" customWidth="1"/>
@@ -1415,73 +1976,731 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <f ca="1">TODAY()</f>
         <v>46222</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="str">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="F5" s="3" t="str">
         <f ca="1">IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
         <v>PAGO</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <f ca="1">TODAY()</f>
         <v>46222</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6">
+        <v>217311</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46216</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="4">
+        <v>46208</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="6">
+        <v>452135</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>46217</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6">
+        <v>155331</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46218</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>46171</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6">
+        <v>65169</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" ref="G9:G11" ca="1" si="0">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>46234</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="6">
+        <v>190566</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>46222</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>46182</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="6">
+        <v>269948</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>46222</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>46240</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6">
+        <v>498749</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46235</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>46261</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="6">
+        <v>316793</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46261</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>46173</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6">
+        <v>249298</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46174</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>46212</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="6">
+        <v>331687</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46208</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="6">
+        <v>128638</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" ref="G16:G17" ca="1" si="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6">
+        <v>256332</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>46211</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6">
+        <v>407113</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46206</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="6">
+        <v>474394</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46199</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>46232</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="6">
+        <v>35608</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46232</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>46178</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="6">
+        <v>457593</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46173</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>46264</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="6">
+        <v>306694</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" ref="G22:G24" ca="1" si="2">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>46211</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6">
+        <v>479918</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>46222</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="4">
+        <v>46248</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="6">
+        <v>357209</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" ca="1" si="2"/>
+        <v>46222</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>46260</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="6">
+        <v>227667</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46258</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="4">
+        <v>46252</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="6">
+        <v>276131</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46254</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="4">
+        <v>46248</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="6">
+        <v>486368</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46244</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="6">
+        <v>497059</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>46251</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="6">
+        <v>472564</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46250</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>46183</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="6">
+        <v>290965</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" ref="G30:G31" ca="1" si="3">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6">
+        <v>393238</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" ca="1" si="3"/>
+        <v>46222</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+  <conditionalFormatting sqref="F5:F31">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+      <formula>"PAGO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+      <formula>"PENDENTE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
-      <formula>"PENDENTE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
-      <formula>"PAGO"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H31">
       <formula1>"BOLETO,TRANSFERENCIA,PIX,DEBITO,CREDITO,DINHEIRO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4">
-      <formula1>"MORADIA,ALIMENTAÇÃO,TRANSPORTE,PESSOAL,ADMINISTRATIVO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1495,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
@@ -1513,68 +2732,680 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="7">
+      <c r="B4" s="11">
         <f ca="1">TODAY()</f>
         <v>46222</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="str">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="str">
         <f ca="1">IF(G4&lt;&gt;"","PAGO",IF(B4&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
         <v>PAGO</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="13">
         <f ca="1">TODAY()</f>
         <v>46222</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="14">
+        <v>46281</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="15">
+        <v>99157</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="16">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="14">
+        <v>46257</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1137025</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="16">
+        <v>46255</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="14">
+        <v>46169</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="15">
+        <v>1001343</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="16">
+        <v>46167</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="14">
+        <v>46273</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="15">
+        <v>374734</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="16">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="14">
+        <v>46261</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="15">
+        <v>971237</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="16">
+        <v>46257</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="14">
+        <v>46167</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="15">
+        <v>1282241</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="16">
+        <v>46169</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="14">
+        <v>46228</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="15">
+        <v>278593</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="16">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="14">
+        <v>46278</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="15">
+        <v>1293239</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="16">
+        <v>46279</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="14">
+        <v>46280</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="15">
+        <v>12266</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="16">
+        <v>46281</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="14">
+        <v>46267</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="15">
+        <v>147901</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="16">
+        <v>46263</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>46177</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="15">
+        <v>561159</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="16">
+        <v>46177</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="14">
+        <v>46247</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="15">
+        <v>71884</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="16">
+        <v>46249</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="14">
+        <v>46223</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="15">
+        <v>44260</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="16">
+        <v>46221</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="14">
+        <v>46219</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="15">
+        <v>607481</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="16">
+        <v>46220</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="14">
+        <v>46254</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="15">
+        <v>1337831</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="16">
+        <f ca="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="14">
+        <v>46179</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="15">
+        <v>522722</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="16">
+        <v>46181</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="14">
+        <v>46208</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="15">
+        <v>922892</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="16">
+        <v>46207</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="14">
+        <v>46170</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="15">
+        <v>1393655</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="16">
+        <v>46172</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="14">
+        <v>46275</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="15">
+        <v>377976</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="16">
+        <f t="shared" ref="G23:G24" ca="1" si="0">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="14">
+        <v>46263</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="15">
+        <v>1468989</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="16">
+        <f t="shared" ca="1" si="0"/>
+        <v>46222</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="14">
+        <v>46232</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="15">
+        <v>643132</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="16">
+        <v>46231</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="14">
+        <v>46248</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="15">
+        <v>890403</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="16">
+        <f t="shared" ref="G26:G28" ca="1" si="1">TODAY()</f>
+        <v>46222</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="14">
+        <v>46185</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="15">
+        <v>159442</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="14">
+        <v>46176</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="15">
+        <v>955553</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="16">
+        <f t="shared" ca="1" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F4">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+  <conditionalFormatting sqref="F4:F28">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"PAGO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"PENDENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3">
-      <formula1>"MORADIA,ALIMENTAÇÃO,TRANSPORTE,PESSOAL,ADMINISTRATIVO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H28">
       <formula1>"BOLETO,TRANSFERENCIA,PIX,DEBITO,CREDITO,DINHEIRO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
+++ b/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Github\Portfolio\Portfólio\Excel\excel-dashboard-financeiro\Dashboard Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12990" windowHeight="5865" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12990" windowHeight="5865"/>
   </bookViews>
   <sheets>
     <sheet name="CONTAS A PAGAR" sheetId="5" r:id="rId1"/>
@@ -17,6 +17,10 @@
     <sheet name="ANALISES" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <pivotCaches>
+    <pivotCache cacheId="31" r:id="rId4"/>
+    <pivotCache cacheId="35" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="73">
   <si>
     <t>CONTAS A RECEBER</t>
   </si>
@@ -70,9 +74,6 @@
     <t>Conta de Luz</t>
   </si>
   <si>
-    <t>Pago</t>
-  </si>
-  <si>
     <t>Cartão de Crédito</t>
   </si>
   <si>
@@ -85,9 +86,6 @@
     <t>Hospedagem de Site</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>Marketing</t>
   </si>
   <si>
@@ -215,16 +213,53 @@
   </si>
   <si>
     <t>Curso de Treinamento</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>mai</t>
+  </si>
+  <si>
+    <t>jun</t>
+  </si>
+  <si>
+    <t>jul</t>
+  </si>
+  <si>
+    <t>ago</t>
+  </si>
+  <si>
+    <t>Rótulos de Coluna</t>
+  </si>
+  <si>
+    <t>PAGO</t>
+  </si>
+  <si>
+    <t>Soma de VALOR A PAGAR</t>
+  </si>
+  <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>ATRASADO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,6 +296,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -282,12 +336,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -344,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -363,31 +426,62 @@
     <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" pivotButton="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -395,7 +489,468 @@
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="137">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="double">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -550,6 +1105,39 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="9"/>
         </left>
@@ -646,41 +1234,6 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="9"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <fill>
         <patternFill patternType="none">
@@ -696,6 +1249,407 @@
           <color theme="9"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="3"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="double">
+          <color theme="4"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -749,66 +1703,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -832,36 +1726,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1408,14 +2272,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>522144</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1386020</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>64943</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>258908</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>641954</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>569768</xdr:rowOff>
     </xdr:to>
@@ -1491,14 +2355,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>101313</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>124042</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>49357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>444213</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>259024</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>554182</xdr:rowOff>
     </xdr:to>
@@ -1570,14 +2434,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>357621</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>785346</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>45893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>94385</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>683425</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>550718</xdr:rowOff>
     </xdr:to>
@@ -1654,43 +2518,2639 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="46223.912276504627" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="27">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Tabela1"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="DATA DE VENCIMENTO" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-29T00:00:00" maxDate="2026-08-31T00:00:00" count="23">
+        <d v="2026-07-20T00:00:00"/>
+        <d v="2026-07-17T00:00:00"/>
+        <d v="2026-07-05T00:00:00"/>
+        <d v="2026-07-14T00:00:00"/>
+        <d v="2026-05-29T00:00:00"/>
+        <d v="2026-07-31T00:00:00"/>
+        <d v="2026-06-09T00:00:00"/>
+        <d v="2026-08-06T00:00:00"/>
+        <d v="2026-08-27T00:00:00"/>
+        <d v="2026-05-31T00:00:00"/>
+        <d v="2026-07-09T00:00:00"/>
+        <d v="2026-06-19T00:00:00"/>
+        <d v="2026-07-08T00:00:00"/>
+        <d v="2026-06-29T00:00:00"/>
+        <d v="2026-07-29T00:00:00"/>
+        <d v="2026-06-05T00:00:00"/>
+        <d v="2026-08-30T00:00:00"/>
+        <d v="2026-08-14T00:00:00"/>
+        <d v="2026-08-26T00:00:00"/>
+        <d v="2026-08-18T00:00:00"/>
+        <d v="2026-06-26T00:00:00"/>
+        <d v="2026-08-17T00:00:00"/>
+        <d v="2026-06-10T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="8" base="0">
+        <rangePr groupBy="days" startDate="2026-05-29T00:00:00" endDate="2026-08-31T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;29/05/2026"/>
+          <s v="01/jan"/>
+          <s v="02/jan"/>
+          <s v="03/jan"/>
+          <s v="04/jan"/>
+          <s v="05/jan"/>
+          <s v="06/jan"/>
+          <s v="07/jan"/>
+          <s v="08/jan"/>
+          <s v="09/jan"/>
+          <s v="10/jan"/>
+          <s v="11/jan"/>
+          <s v="12/jan"/>
+          <s v="13/jan"/>
+          <s v="14/jan"/>
+          <s v="15/jan"/>
+          <s v="16/jan"/>
+          <s v="17/jan"/>
+          <s v="18/jan"/>
+          <s v="19/jan"/>
+          <s v="20/jan"/>
+          <s v="21/jan"/>
+          <s v="22/jan"/>
+          <s v="23/jan"/>
+          <s v="24/jan"/>
+          <s v="25/jan"/>
+          <s v="26/jan"/>
+          <s v="27/jan"/>
+          <s v="28/jan"/>
+          <s v="29/jan"/>
+          <s v="30/jan"/>
+          <s v="31/jan"/>
+          <s v="01/fev"/>
+          <s v="02/fev"/>
+          <s v="03/fev"/>
+          <s v="04/fev"/>
+          <s v="05/fev"/>
+          <s v="06/fev"/>
+          <s v="07/fev"/>
+          <s v="08/fev"/>
+          <s v="09/fev"/>
+          <s v="10/fev"/>
+          <s v="11/fev"/>
+          <s v="12/fev"/>
+          <s v="13/fev"/>
+          <s v="14/fev"/>
+          <s v="15/fev"/>
+          <s v="16/fev"/>
+          <s v="17/fev"/>
+          <s v="18/fev"/>
+          <s v="19/fev"/>
+          <s v="20/fev"/>
+          <s v="21/fev"/>
+          <s v="22/fev"/>
+          <s v="23/fev"/>
+          <s v="24/fev"/>
+          <s v="25/fev"/>
+          <s v="26/fev"/>
+          <s v="27/fev"/>
+          <s v="28/fev"/>
+          <s v="29/fev"/>
+          <s v="01/mar"/>
+          <s v="02/mar"/>
+          <s v="03/mar"/>
+          <s v="04/mar"/>
+          <s v="05/mar"/>
+          <s v="06/mar"/>
+          <s v="07/mar"/>
+          <s v="08/mar"/>
+          <s v="09/mar"/>
+          <s v="10/mar"/>
+          <s v="11/mar"/>
+          <s v="12/mar"/>
+          <s v="13/mar"/>
+          <s v="14/mar"/>
+          <s v="15/mar"/>
+          <s v="16/mar"/>
+          <s v="17/mar"/>
+          <s v="18/mar"/>
+          <s v="19/mar"/>
+          <s v="20/mar"/>
+          <s v="21/mar"/>
+          <s v="22/mar"/>
+          <s v="23/mar"/>
+          <s v="24/mar"/>
+          <s v="25/mar"/>
+          <s v="26/mar"/>
+          <s v="27/mar"/>
+          <s v="28/mar"/>
+          <s v="29/mar"/>
+          <s v="30/mar"/>
+          <s v="31/mar"/>
+          <s v="01/abr"/>
+          <s v="02/abr"/>
+          <s v="03/abr"/>
+          <s v="04/abr"/>
+          <s v="05/abr"/>
+          <s v="06/abr"/>
+          <s v="07/abr"/>
+          <s v="08/abr"/>
+          <s v="09/abr"/>
+          <s v="10/abr"/>
+          <s v="11/abr"/>
+          <s v="12/abr"/>
+          <s v="13/abr"/>
+          <s v="14/abr"/>
+          <s v="15/abr"/>
+          <s v="16/abr"/>
+          <s v="17/abr"/>
+          <s v="18/abr"/>
+          <s v="19/abr"/>
+          <s v="20/abr"/>
+          <s v="21/abr"/>
+          <s v="22/abr"/>
+          <s v="23/abr"/>
+          <s v="24/abr"/>
+          <s v="25/abr"/>
+          <s v="26/abr"/>
+          <s v="27/abr"/>
+          <s v="28/abr"/>
+          <s v="29/abr"/>
+          <s v="30/abr"/>
+          <s v="01/mai"/>
+          <s v="02/mai"/>
+          <s v="03/mai"/>
+          <s v="04/mai"/>
+          <s v="05/mai"/>
+          <s v="06/mai"/>
+          <s v="07/mai"/>
+          <s v="08/mai"/>
+          <s v="09/mai"/>
+          <s v="10/mai"/>
+          <s v="11/mai"/>
+          <s v="12/mai"/>
+          <s v="13/mai"/>
+          <s v="14/mai"/>
+          <s v="15/mai"/>
+          <s v="16/mai"/>
+          <s v="17/mai"/>
+          <s v="18/mai"/>
+          <s v="19/mai"/>
+          <s v="20/mai"/>
+          <s v="21/mai"/>
+          <s v="22/mai"/>
+          <s v="23/mai"/>
+          <s v="24/mai"/>
+          <s v="25/mai"/>
+          <s v="26/mai"/>
+          <s v="27/mai"/>
+          <s v="28/mai"/>
+          <s v="29/mai"/>
+          <s v="30/mai"/>
+          <s v="31/mai"/>
+          <s v="01/jun"/>
+          <s v="02/jun"/>
+          <s v="03/jun"/>
+          <s v="04/jun"/>
+          <s v="05/jun"/>
+          <s v="06/jun"/>
+          <s v="07/jun"/>
+          <s v="08/jun"/>
+          <s v="09/jun"/>
+          <s v="10/jun"/>
+          <s v="11/jun"/>
+          <s v="12/jun"/>
+          <s v="13/jun"/>
+          <s v="14/jun"/>
+          <s v="15/jun"/>
+          <s v="16/jun"/>
+          <s v="17/jun"/>
+          <s v="18/jun"/>
+          <s v="19/jun"/>
+          <s v="20/jun"/>
+          <s v="21/jun"/>
+          <s v="22/jun"/>
+          <s v="23/jun"/>
+          <s v="24/jun"/>
+          <s v="25/jun"/>
+          <s v="26/jun"/>
+          <s v="27/jun"/>
+          <s v="28/jun"/>
+          <s v="29/jun"/>
+          <s v="30/jun"/>
+          <s v="01/jul"/>
+          <s v="02/jul"/>
+          <s v="03/jul"/>
+          <s v="04/jul"/>
+          <s v="05/jul"/>
+          <s v="06/jul"/>
+          <s v="07/jul"/>
+          <s v="08/jul"/>
+          <s v="09/jul"/>
+          <s v="10/jul"/>
+          <s v="11/jul"/>
+          <s v="12/jul"/>
+          <s v="13/jul"/>
+          <s v="14/jul"/>
+          <s v="15/jul"/>
+          <s v="16/jul"/>
+          <s v="17/jul"/>
+          <s v="18/jul"/>
+          <s v="19/jul"/>
+          <s v="20/jul"/>
+          <s v="21/jul"/>
+          <s v="22/jul"/>
+          <s v="23/jul"/>
+          <s v="24/jul"/>
+          <s v="25/jul"/>
+          <s v="26/jul"/>
+          <s v="27/jul"/>
+          <s v="28/jul"/>
+          <s v="29/jul"/>
+          <s v="30/jul"/>
+          <s v="31/jul"/>
+          <s v="01/ago"/>
+          <s v="02/ago"/>
+          <s v="03/ago"/>
+          <s v="04/ago"/>
+          <s v="05/ago"/>
+          <s v="06/ago"/>
+          <s v="07/ago"/>
+          <s v="08/ago"/>
+          <s v="09/ago"/>
+          <s v="10/ago"/>
+          <s v="11/ago"/>
+          <s v="12/ago"/>
+          <s v="13/ago"/>
+          <s v="14/ago"/>
+          <s v="15/ago"/>
+          <s v="16/ago"/>
+          <s v="17/ago"/>
+          <s v="18/ago"/>
+          <s v="19/ago"/>
+          <s v="20/ago"/>
+          <s v="21/ago"/>
+          <s v="22/ago"/>
+          <s v="23/ago"/>
+          <s v="24/ago"/>
+          <s v="25/ago"/>
+          <s v="26/ago"/>
+          <s v="27/ago"/>
+          <s v="28/ago"/>
+          <s v="29/ago"/>
+          <s v="30/ago"/>
+          <s v="31/ago"/>
+          <s v="01/set"/>
+          <s v="02/set"/>
+          <s v="03/set"/>
+          <s v="04/set"/>
+          <s v="05/set"/>
+          <s v="06/set"/>
+          <s v="07/set"/>
+          <s v="08/set"/>
+          <s v="09/set"/>
+          <s v="10/set"/>
+          <s v="11/set"/>
+          <s v="12/set"/>
+          <s v="13/set"/>
+          <s v="14/set"/>
+          <s v="15/set"/>
+          <s v="16/set"/>
+          <s v="17/set"/>
+          <s v="18/set"/>
+          <s v="19/set"/>
+          <s v="20/set"/>
+          <s v="21/set"/>
+          <s v="22/set"/>
+          <s v="23/set"/>
+          <s v="24/set"/>
+          <s v="25/set"/>
+          <s v="26/set"/>
+          <s v="27/set"/>
+          <s v="28/set"/>
+          <s v="29/set"/>
+          <s v="30/set"/>
+          <s v="01/out"/>
+          <s v="02/out"/>
+          <s v="03/out"/>
+          <s v="04/out"/>
+          <s v="05/out"/>
+          <s v="06/out"/>
+          <s v="07/out"/>
+          <s v="08/out"/>
+          <s v="09/out"/>
+          <s v="10/out"/>
+          <s v="11/out"/>
+          <s v="12/out"/>
+          <s v="13/out"/>
+          <s v="14/out"/>
+          <s v="15/out"/>
+          <s v="16/out"/>
+          <s v="17/out"/>
+          <s v="18/out"/>
+          <s v="19/out"/>
+          <s v="20/out"/>
+          <s v="21/out"/>
+          <s v="22/out"/>
+          <s v="23/out"/>
+          <s v="24/out"/>
+          <s v="25/out"/>
+          <s v="26/out"/>
+          <s v="27/out"/>
+          <s v="28/out"/>
+          <s v="29/out"/>
+          <s v="30/out"/>
+          <s v="31/out"/>
+          <s v="01/nov"/>
+          <s v="02/nov"/>
+          <s v="03/nov"/>
+          <s v="04/nov"/>
+          <s v="05/nov"/>
+          <s v="06/nov"/>
+          <s v="07/nov"/>
+          <s v="08/nov"/>
+          <s v="09/nov"/>
+          <s v="10/nov"/>
+          <s v="11/nov"/>
+          <s v="12/nov"/>
+          <s v="13/nov"/>
+          <s v="14/nov"/>
+          <s v="15/nov"/>
+          <s v="16/nov"/>
+          <s v="17/nov"/>
+          <s v="18/nov"/>
+          <s v="19/nov"/>
+          <s v="20/nov"/>
+          <s v="21/nov"/>
+          <s v="22/nov"/>
+          <s v="23/nov"/>
+          <s v="24/nov"/>
+          <s v="25/nov"/>
+          <s v="26/nov"/>
+          <s v="27/nov"/>
+          <s v="28/nov"/>
+          <s v="29/nov"/>
+          <s v="30/nov"/>
+          <s v="01/dez"/>
+          <s v="02/dez"/>
+          <s v="03/dez"/>
+          <s v="04/dez"/>
+          <s v="05/dez"/>
+          <s v="06/dez"/>
+          <s v="07/dez"/>
+          <s v="08/dez"/>
+          <s v="09/dez"/>
+          <s v="10/dez"/>
+          <s v="11/dez"/>
+          <s v="12/dez"/>
+          <s v="13/dez"/>
+          <s v="14/dez"/>
+          <s v="15/dez"/>
+          <s v="16/dez"/>
+          <s v="17/dez"/>
+          <s v="18/dez"/>
+          <s v="19/dez"/>
+          <s v="20/dez"/>
+          <s v="21/dez"/>
+          <s v="22/dez"/>
+          <s v="23/dez"/>
+          <s v="24/dez"/>
+          <s v="25/dez"/>
+          <s v="26/dez"/>
+          <s v="27/dez"/>
+          <s v="28/dez"/>
+          <s v="29/dez"/>
+          <s v="30/dez"/>
+          <s v="31/dez"/>
+          <s v="&gt;31/08/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="FORNECEDOR" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="DESCRIÇÃO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="VALOR A PAGAR" numFmtId="44">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="35608" maxValue="498749"/>
+    </cacheField>
+    <cacheField name="STATUS" numFmtId="0">
+      <sharedItems count="3">
+        <s v="PENDENTE"/>
+        <s v="PAGO"/>
+        <s v="ATRASADO"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DATA DE PAGAMENTO" numFmtId="14">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-05-31T00:00:00" maxDate="2026-08-28T00:00:00"/>
+    </cacheField>
+    <cacheField name="TIPO DE PAGAMENTO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="CENTRO DE CUSTO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Meses" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2026-05-29T00:00:00" endDate="2026-08-31T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;29/05/2026"/>
+          <s v="jan"/>
+          <s v="fev"/>
+          <s v="mar"/>
+          <s v="abr"/>
+          <s v="mai"/>
+          <s v="jun"/>
+          <s v="jul"/>
+          <s v="ago"/>
+          <s v="set"/>
+          <s v="out"/>
+          <s v="nov"/>
+          <s v="dez"/>
+          <s v="&gt;31/08/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="46223.91233298611" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="25">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Tabela4"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="DATA DE VENCIMENTO" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-25T00:00:00" maxDate="2026-09-17T00:00:00" count="24">
+        <d v="2026-07-20T00:00:00"/>
+        <d v="2026-09-16T00:00:00"/>
+        <d v="2026-08-23T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-09-08T00:00:00"/>
+        <d v="2026-08-27T00:00:00"/>
+        <d v="2026-05-25T00:00:00"/>
+        <d v="2026-07-25T00:00:00"/>
+        <d v="2026-09-13T00:00:00"/>
+        <d v="2026-09-15T00:00:00"/>
+        <d v="2026-09-02T00:00:00"/>
+        <d v="2026-06-04T00:00:00"/>
+        <d v="2026-08-13T00:00:00"/>
+        <d v="2026-07-16T00:00:00"/>
+        <d v="2026-08-20T00:00:00"/>
+        <d v="2026-06-06T00:00:00"/>
+        <d v="2026-07-05T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-09-10T00:00:00"/>
+        <d v="2026-08-29T00:00:00"/>
+        <d v="2026-07-29T00:00:00"/>
+        <d v="2026-08-14T00:00:00"/>
+        <d v="2026-06-12T00:00:00"/>
+        <d v="2026-06-03T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="8" base="0">
+        <rangePr groupBy="days" startDate="2026-05-25T00:00:00" endDate="2026-09-17T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;25/05/2026"/>
+          <s v="01/jan"/>
+          <s v="02/jan"/>
+          <s v="03/jan"/>
+          <s v="04/jan"/>
+          <s v="05/jan"/>
+          <s v="06/jan"/>
+          <s v="07/jan"/>
+          <s v="08/jan"/>
+          <s v="09/jan"/>
+          <s v="10/jan"/>
+          <s v="11/jan"/>
+          <s v="12/jan"/>
+          <s v="13/jan"/>
+          <s v="14/jan"/>
+          <s v="15/jan"/>
+          <s v="16/jan"/>
+          <s v="17/jan"/>
+          <s v="18/jan"/>
+          <s v="19/jan"/>
+          <s v="20/jan"/>
+          <s v="21/jan"/>
+          <s v="22/jan"/>
+          <s v="23/jan"/>
+          <s v="24/jan"/>
+          <s v="25/jan"/>
+          <s v="26/jan"/>
+          <s v="27/jan"/>
+          <s v="28/jan"/>
+          <s v="29/jan"/>
+          <s v="30/jan"/>
+          <s v="31/jan"/>
+          <s v="01/fev"/>
+          <s v="02/fev"/>
+          <s v="03/fev"/>
+          <s v="04/fev"/>
+          <s v="05/fev"/>
+          <s v="06/fev"/>
+          <s v="07/fev"/>
+          <s v="08/fev"/>
+          <s v="09/fev"/>
+          <s v="10/fev"/>
+          <s v="11/fev"/>
+          <s v="12/fev"/>
+          <s v="13/fev"/>
+          <s v="14/fev"/>
+          <s v="15/fev"/>
+          <s v="16/fev"/>
+          <s v="17/fev"/>
+          <s v="18/fev"/>
+          <s v="19/fev"/>
+          <s v="20/fev"/>
+          <s v="21/fev"/>
+          <s v="22/fev"/>
+          <s v="23/fev"/>
+          <s v="24/fev"/>
+          <s v="25/fev"/>
+          <s v="26/fev"/>
+          <s v="27/fev"/>
+          <s v="28/fev"/>
+          <s v="29/fev"/>
+          <s v="01/mar"/>
+          <s v="02/mar"/>
+          <s v="03/mar"/>
+          <s v="04/mar"/>
+          <s v="05/mar"/>
+          <s v="06/mar"/>
+          <s v="07/mar"/>
+          <s v="08/mar"/>
+          <s v="09/mar"/>
+          <s v="10/mar"/>
+          <s v="11/mar"/>
+          <s v="12/mar"/>
+          <s v="13/mar"/>
+          <s v="14/mar"/>
+          <s v="15/mar"/>
+          <s v="16/mar"/>
+          <s v="17/mar"/>
+          <s v="18/mar"/>
+          <s v="19/mar"/>
+          <s v="20/mar"/>
+          <s v="21/mar"/>
+          <s v="22/mar"/>
+          <s v="23/mar"/>
+          <s v="24/mar"/>
+          <s v="25/mar"/>
+          <s v="26/mar"/>
+          <s v="27/mar"/>
+          <s v="28/mar"/>
+          <s v="29/mar"/>
+          <s v="30/mar"/>
+          <s v="31/mar"/>
+          <s v="01/abr"/>
+          <s v="02/abr"/>
+          <s v="03/abr"/>
+          <s v="04/abr"/>
+          <s v="05/abr"/>
+          <s v="06/abr"/>
+          <s v="07/abr"/>
+          <s v="08/abr"/>
+          <s v="09/abr"/>
+          <s v="10/abr"/>
+          <s v="11/abr"/>
+          <s v="12/abr"/>
+          <s v="13/abr"/>
+          <s v="14/abr"/>
+          <s v="15/abr"/>
+          <s v="16/abr"/>
+          <s v="17/abr"/>
+          <s v="18/abr"/>
+          <s v="19/abr"/>
+          <s v="20/abr"/>
+          <s v="21/abr"/>
+          <s v="22/abr"/>
+          <s v="23/abr"/>
+          <s v="24/abr"/>
+          <s v="25/abr"/>
+          <s v="26/abr"/>
+          <s v="27/abr"/>
+          <s v="28/abr"/>
+          <s v="29/abr"/>
+          <s v="30/abr"/>
+          <s v="01/mai"/>
+          <s v="02/mai"/>
+          <s v="03/mai"/>
+          <s v="04/mai"/>
+          <s v="05/mai"/>
+          <s v="06/mai"/>
+          <s v="07/mai"/>
+          <s v="08/mai"/>
+          <s v="09/mai"/>
+          <s v="10/mai"/>
+          <s v="11/mai"/>
+          <s v="12/mai"/>
+          <s v="13/mai"/>
+          <s v="14/mai"/>
+          <s v="15/mai"/>
+          <s v="16/mai"/>
+          <s v="17/mai"/>
+          <s v="18/mai"/>
+          <s v="19/mai"/>
+          <s v="20/mai"/>
+          <s v="21/mai"/>
+          <s v="22/mai"/>
+          <s v="23/mai"/>
+          <s v="24/mai"/>
+          <s v="25/mai"/>
+          <s v="26/mai"/>
+          <s v="27/mai"/>
+          <s v="28/mai"/>
+          <s v="29/mai"/>
+          <s v="30/mai"/>
+          <s v="31/mai"/>
+          <s v="01/jun"/>
+          <s v="02/jun"/>
+          <s v="03/jun"/>
+          <s v="04/jun"/>
+          <s v="05/jun"/>
+          <s v="06/jun"/>
+          <s v="07/jun"/>
+          <s v="08/jun"/>
+          <s v="09/jun"/>
+          <s v="10/jun"/>
+          <s v="11/jun"/>
+          <s v="12/jun"/>
+          <s v="13/jun"/>
+          <s v="14/jun"/>
+          <s v="15/jun"/>
+          <s v="16/jun"/>
+          <s v="17/jun"/>
+          <s v="18/jun"/>
+          <s v="19/jun"/>
+          <s v="20/jun"/>
+          <s v="21/jun"/>
+          <s v="22/jun"/>
+          <s v="23/jun"/>
+          <s v="24/jun"/>
+          <s v="25/jun"/>
+          <s v="26/jun"/>
+          <s v="27/jun"/>
+          <s v="28/jun"/>
+          <s v="29/jun"/>
+          <s v="30/jun"/>
+          <s v="01/jul"/>
+          <s v="02/jul"/>
+          <s v="03/jul"/>
+          <s v="04/jul"/>
+          <s v="05/jul"/>
+          <s v="06/jul"/>
+          <s v="07/jul"/>
+          <s v="08/jul"/>
+          <s v="09/jul"/>
+          <s v="10/jul"/>
+          <s v="11/jul"/>
+          <s v="12/jul"/>
+          <s v="13/jul"/>
+          <s v="14/jul"/>
+          <s v="15/jul"/>
+          <s v="16/jul"/>
+          <s v="17/jul"/>
+          <s v="18/jul"/>
+          <s v="19/jul"/>
+          <s v="20/jul"/>
+          <s v="21/jul"/>
+          <s v="22/jul"/>
+          <s v="23/jul"/>
+          <s v="24/jul"/>
+          <s v="25/jul"/>
+          <s v="26/jul"/>
+          <s v="27/jul"/>
+          <s v="28/jul"/>
+          <s v="29/jul"/>
+          <s v="30/jul"/>
+          <s v="31/jul"/>
+          <s v="01/ago"/>
+          <s v="02/ago"/>
+          <s v="03/ago"/>
+          <s v="04/ago"/>
+          <s v="05/ago"/>
+          <s v="06/ago"/>
+          <s v="07/ago"/>
+          <s v="08/ago"/>
+          <s v="09/ago"/>
+          <s v="10/ago"/>
+          <s v="11/ago"/>
+          <s v="12/ago"/>
+          <s v="13/ago"/>
+          <s v="14/ago"/>
+          <s v="15/ago"/>
+          <s v="16/ago"/>
+          <s v="17/ago"/>
+          <s v="18/ago"/>
+          <s v="19/ago"/>
+          <s v="20/ago"/>
+          <s v="21/ago"/>
+          <s v="22/ago"/>
+          <s v="23/ago"/>
+          <s v="24/ago"/>
+          <s v="25/ago"/>
+          <s v="26/ago"/>
+          <s v="27/ago"/>
+          <s v="28/ago"/>
+          <s v="29/ago"/>
+          <s v="30/ago"/>
+          <s v="31/ago"/>
+          <s v="01/set"/>
+          <s v="02/set"/>
+          <s v="03/set"/>
+          <s v="04/set"/>
+          <s v="05/set"/>
+          <s v="06/set"/>
+          <s v="07/set"/>
+          <s v="08/set"/>
+          <s v="09/set"/>
+          <s v="10/set"/>
+          <s v="11/set"/>
+          <s v="12/set"/>
+          <s v="13/set"/>
+          <s v="14/set"/>
+          <s v="15/set"/>
+          <s v="16/set"/>
+          <s v="17/set"/>
+          <s v="18/set"/>
+          <s v="19/set"/>
+          <s v="20/set"/>
+          <s v="21/set"/>
+          <s v="22/set"/>
+          <s v="23/set"/>
+          <s v="24/set"/>
+          <s v="25/set"/>
+          <s v="26/set"/>
+          <s v="27/set"/>
+          <s v="28/set"/>
+          <s v="29/set"/>
+          <s v="30/set"/>
+          <s v="01/out"/>
+          <s v="02/out"/>
+          <s v="03/out"/>
+          <s v="04/out"/>
+          <s v="05/out"/>
+          <s v="06/out"/>
+          <s v="07/out"/>
+          <s v="08/out"/>
+          <s v="09/out"/>
+          <s v="10/out"/>
+          <s v="11/out"/>
+          <s v="12/out"/>
+          <s v="13/out"/>
+          <s v="14/out"/>
+          <s v="15/out"/>
+          <s v="16/out"/>
+          <s v="17/out"/>
+          <s v="18/out"/>
+          <s v="19/out"/>
+          <s v="20/out"/>
+          <s v="21/out"/>
+          <s v="22/out"/>
+          <s v="23/out"/>
+          <s v="24/out"/>
+          <s v="25/out"/>
+          <s v="26/out"/>
+          <s v="27/out"/>
+          <s v="28/out"/>
+          <s v="29/out"/>
+          <s v="30/out"/>
+          <s v="31/out"/>
+          <s v="01/nov"/>
+          <s v="02/nov"/>
+          <s v="03/nov"/>
+          <s v="04/nov"/>
+          <s v="05/nov"/>
+          <s v="06/nov"/>
+          <s v="07/nov"/>
+          <s v="08/nov"/>
+          <s v="09/nov"/>
+          <s v="10/nov"/>
+          <s v="11/nov"/>
+          <s v="12/nov"/>
+          <s v="13/nov"/>
+          <s v="14/nov"/>
+          <s v="15/nov"/>
+          <s v="16/nov"/>
+          <s v="17/nov"/>
+          <s v="18/nov"/>
+          <s v="19/nov"/>
+          <s v="20/nov"/>
+          <s v="21/nov"/>
+          <s v="22/nov"/>
+          <s v="23/nov"/>
+          <s v="24/nov"/>
+          <s v="25/nov"/>
+          <s v="26/nov"/>
+          <s v="27/nov"/>
+          <s v="28/nov"/>
+          <s v="29/nov"/>
+          <s v="30/nov"/>
+          <s v="01/dez"/>
+          <s v="02/dez"/>
+          <s v="03/dez"/>
+          <s v="04/dez"/>
+          <s v="05/dez"/>
+          <s v="06/dez"/>
+          <s v="07/dez"/>
+          <s v="08/dez"/>
+          <s v="09/dez"/>
+          <s v="10/dez"/>
+          <s v="11/dez"/>
+          <s v="12/dez"/>
+          <s v="13/dez"/>
+          <s v="14/dez"/>
+          <s v="15/dez"/>
+          <s v="16/dez"/>
+          <s v="17/dez"/>
+          <s v="18/dez"/>
+          <s v="19/dez"/>
+          <s v="20/dez"/>
+          <s v="21/dez"/>
+          <s v="22/dez"/>
+          <s v="23/dez"/>
+          <s v="24/dez"/>
+          <s v="25/dez"/>
+          <s v="26/dez"/>
+          <s v="27/dez"/>
+          <s v="28/dez"/>
+          <s v="29/dez"/>
+          <s v="30/dez"/>
+          <s v="31/dez"/>
+          <s v="&gt;17/09/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="CLIENTE" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="DESCRIÇÃO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="VALOR A PAGAR" numFmtId="44">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="12266" maxValue="1468989"/>
+    </cacheField>
+    <cacheField name="STATUS" numFmtId="0">
+      <sharedItems count="3">
+        <s v="PAGO"/>
+        <s v="PENDENTE"/>
+        <s v="ATRASADO"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="DATA DE PAGAMENTO" numFmtId="14">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-05-25T00:00:00" maxDate="2026-09-17T00:00:00"/>
+    </cacheField>
+    <cacheField name="TIPO DE PAGAMENTO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="CENTRO DE CUSTO" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Meses" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2026-05-25T00:00:00" endDate="2026-09-17T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;25/05/2026"/>
+          <s v="jan"/>
+          <s v="fev"/>
+          <s v="mar"/>
+          <s v="abr"/>
+          <s v="mai"/>
+          <s v="jun"/>
+          <s v="jul"/>
+          <s v="ago"/>
+          <s v="set"/>
+          <s v="out"/>
+          <s v="nov"/>
+          <s v="dez"/>
+          <s v="&gt;17/09/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="27">
+  <r>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Gráfica Rápida"/>
+    <s v="Conta de Luz"/>
+    <n v="217311"/>
+    <x v="1"/>
+    <d v="2026-07-13T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Hospedagem de Site"/>
+    <n v="452135"/>
+    <x v="1"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Consultoria XPTO"/>
+    <s v="Material de Escritório"/>
+    <n v="155331"/>
+    <x v="1"/>
+    <d v="2026-07-15T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="Vendas"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Limpeza &amp; Cia"/>
+    <s v="Assinatura de Software"/>
+    <n v="65169"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Energia S.A."/>
+    <s v="Seguro Predial"/>
+    <n v="190566"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <s v="Operacional"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="AWS Amazon"/>
+    <s v="Manutenção de Ar-condicionado"/>
+    <n v="269948"/>
+    <x v="1"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Limpeza &amp; Cia"/>
+    <s v="Campanha de Marketing"/>
+    <n v="498749"/>
+    <x v="1"/>
+    <d v="2026-08-01T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="AWS Amazon"/>
+    <s v="Seguro Predial"/>
+    <n v="316793"/>
+    <x v="1"/>
+    <d v="2026-08-27T00:00:00"/>
+    <s v="Pix"/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Papelaria Silva"/>
+    <s v="Conta de Luz"/>
+    <n v="249298"/>
+    <x v="1"/>
+    <d v="2026-06-01T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Serviços de Consultoria"/>
+    <n v="331687"/>
+    <x v="2"/>
+    <m/>
+    <s v="Transferência Bancária"/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Conta de Luz"/>
+    <n v="128638"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="Vendas"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Assinatura de Software"/>
+    <n v="256332"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Limpeza &amp; Cia"/>
+    <s v="Insumos de Produção"/>
+    <n v="407113"/>
+    <x v="1"/>
+    <d v="2026-07-03T00:00:00"/>
+    <s v="Pix"/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Papelaria Silva"/>
+    <s v="Insumos de Produção"/>
+    <n v="474394"/>
+    <x v="1"/>
+    <d v="2026-06-26T00:00:00"/>
+    <s v="Pix"/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Energia S.A."/>
+    <s v="Material de Escritório"/>
+    <n v="35608"/>
+    <x v="1"/>
+    <d v="2026-07-29T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Energia S.A."/>
+    <s v="Seguro Predial"/>
+    <n v="457593"/>
+    <x v="1"/>
+    <d v="2026-05-31T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Seguros Porto"/>
+    <s v="Limpeza Mensal"/>
+    <n v="306694"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Gráfica Rápida"/>
+    <s v="Material de Escritório"/>
+    <n v="479918"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Papelaria Silva"/>
+    <s v="Manutenção de Ar-condicionado"/>
+    <n v="357209"/>
+    <x v="1"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Vendas"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Material de Escritório"/>
+    <n v="227667"/>
+    <x v="1"/>
+    <d v="2026-08-24T00:00:00"/>
+    <s v="Pix"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Gráfica Rápida"/>
+    <s v="Material de Escritório"/>
+    <n v="276131"/>
+    <x v="1"/>
+    <d v="2026-08-20T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Aluguel Imóveis"/>
+    <s v="Limpeza Mensal"/>
+    <n v="486368"/>
+    <x v="1"/>
+    <d v="2026-08-10T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Internet Fibra"/>
+    <s v="Hospedagem de Site"/>
+    <n v="497059"/>
+    <x v="1"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Operacional"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Internet Fibra"/>
+    <s v="Manutenção de Ar-condicionado"/>
+    <n v="472564"/>
+    <x v="1"/>
+    <d v="2026-08-16T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Consultoria XPTO"/>
+    <s v="Serviços de Consultoria"/>
+    <n v="290965"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Papelaria Silva"/>
+    <s v="Insumos de Produção"/>
+    <n v="393238"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="RH"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="25">
+  <r>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Varejo Global"/>
+    <s v="Suporte Premium"/>
+    <n v="99157"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Construtora Alfa"/>
+    <s v="Projeto de Software"/>
+    <n v="1137025"/>
+    <x v="0"/>
+    <d v="2026-08-21T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Supermercado Real"/>
+    <s v="Venda de Equipamento"/>
+    <n v="1001343"/>
+    <x v="0"/>
+    <d v="2026-05-25T00:00:00"/>
+    <s v="Pix"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="João Silva"/>
+    <s v="Manutenção de Sistema"/>
+    <n v="374734"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Academia Fit"/>
+    <s v="Venda de Licença"/>
+    <n v="971237"/>
+    <x v="0"/>
+    <d v="2026-08-23T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Escola Aprender"/>
+    <s v="Desenvolvimento de Site"/>
+    <n v="1282241"/>
+    <x v="0"/>
+    <d v="2026-05-27T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Supermercado Real"/>
+    <s v="Projeto de Software"/>
+    <n v="278593"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Supermercado Real"/>
+    <s v="Venda de Licença"/>
+    <n v="1293239"/>
+    <x v="1"/>
+    <m/>
+    <s v="Cartão de Crédito"/>
+    <s v="Vendas"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Hospital Vida"/>
+    <s v="Consultoria Técnica"/>
+    <n v="12266"/>
+    <x v="0"/>
+    <d v="2026-09-16T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="Operacional"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Escola Aprender"/>
+    <s v="Manutenção de Sistema"/>
+    <n v="147901"/>
+    <x v="0"/>
+    <d v="2026-08-29T00:00:00"/>
+    <s v="Cartão de Crédito"/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Restaurante Sabor"/>
+    <s v="Manutenção de Sistema"/>
+    <n v="561159"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Tech Solutions Ltda"/>
+    <s v="Prestação de Serviço Mensal"/>
+    <n v="71884"/>
+    <x v="0"/>
+    <d v="2026-08-15T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Tech Solutions Ltda"/>
+    <s v="Suporte Premium"/>
+    <n v="44260"/>
+    <x v="0"/>
+    <d v="2026-07-18T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="Operacional"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Hospital Vida"/>
+    <s v="Desenvolvimento de Site"/>
+    <n v="607481"/>
+    <x v="0"/>
+    <d v="2026-07-17T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="Administrativo"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Maria Oliveira"/>
+    <s v="Prestação de Serviço Mensal"/>
+    <n v="1337831"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Construtora Alfa"/>
+    <s v="Curso de Treinamento"/>
+    <n v="522722"/>
+    <x v="0"/>
+    <d v="2026-06-08T00:00:00"/>
+    <s v="Pix"/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Escola Aprender"/>
+    <s v="Venda de Equipamento"/>
+    <n v="922892"/>
+    <x v="0"/>
+    <d v="2026-07-04T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="Operacional"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Supermercado Real"/>
+    <s v="Suporte Premium"/>
+    <n v="1393655"/>
+    <x v="0"/>
+    <d v="2026-05-30T00:00:00"/>
+    <s v="Boleto"/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Varejo Global"/>
+    <s v="Venda de Equipamento"/>
+    <n v="377976"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Construtora Alfa"/>
+    <s v="Projeto de Software"/>
+    <n v="1468989"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="Financeiro"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Escola Aprender"/>
+    <s v="Venda de Equipamento"/>
+    <n v="643132"/>
+    <x v="0"/>
+    <d v="2026-07-28T00:00:00"/>
+    <s v="Transferência Bancária"/>
+    <s v="TI"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Supermercado Real"/>
+    <s v="Venda de Equipamento"/>
+    <n v="890403"/>
+    <x v="0"/>
+    <d v="2026-07-20T00:00:00"/>
+    <m/>
+    <s v="RH"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Tech Solutions Ltda"/>
+    <s v="Prestação de Serviço Mensal"/>
+    <n v="159442"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="Marketing"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Restaurante Sabor"/>
+    <s v="Prestação de Serviço Mensal"/>
+    <n v="955553"/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <s v="Financeiro"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica4" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H4:L11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="8"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de VALOR A PAGAR" fld="3" baseField="8" baseItem="5" numFmtId="44"/>
+  </dataFields>
+  <formats count="11">
+    <format dxfId="88">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="87">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="86">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="85">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="84">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="83">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="82">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="5">
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="81">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="80">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="79">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="66">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium3" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica2" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B4:F10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="8"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de VALOR A PAGAR" fld="3" baseField="8" baseItem="5" numFmtId="164"/>
+  </dataFields>
+  <formats count="40">
+    <format dxfId="116">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="115">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="114">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="113">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="112">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="111">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="110">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="109">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="108">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="107">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="106">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="105">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="104">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="103">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="102">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="101">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="100">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="99">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="98">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="97">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="96">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="95">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="94">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="93">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="92">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="91">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="90">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="89">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="78">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="77">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="76">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="75">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="74">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="73">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="72">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="71">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="70">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="69">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="4">
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="68">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="67">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B4:I31" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B4:I31" headerRowDxfId="136" dataDxfId="135">
   <autoFilter ref="B4:I31"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="DATA DE VENCIMENTO" totalsRowLabel="Total" dataDxfId="35" totalsRowDxfId="17">
+    <tableColumn id="1" name="DATA DE VENCIMENTO" totalsRowLabel="Total" dataDxfId="134" totalsRowDxfId="119">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="FORNECEDOR" dataDxfId="34" totalsRowDxfId="18"/>
-    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="30" totalsRowDxfId="19"/>
-    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="28" totalsRowDxfId="20" dataCellStyle="Moeda"/>
-    <tableColumn id="5" name="STATUS" dataDxfId="29" totalsRowDxfId="21">
+    <tableColumn id="2" name="FORNECEDOR" dataDxfId="133" totalsRowDxfId="120"/>
+    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="129" totalsRowDxfId="121"/>
+    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="127" totalsRowDxfId="122" dataCellStyle="Moeda"/>
+    <tableColumn id="5" name="STATUS" dataDxfId="128" totalsRowDxfId="123">
       <calculatedColumnFormula>IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="33" totalsRowDxfId="22">
+    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="132" totalsRowDxfId="124">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="32" totalsRowDxfId="23"/>
-    <tableColumn id="8" name="CENTRO DE CUSTO" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="24"/>
+    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="131" totalsRowDxfId="125"/>
+    <tableColumn id="8" name="CENTRO DE CUSTO" totalsRowFunction="count" dataDxfId="130" totalsRowDxfId="126"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="B3:I28" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
-  <autoFilter ref="B3:I28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabela4" displayName="Tabela4" ref="B4:I29" totalsRowShown="0" headerRowDxfId="118" dataDxfId="57" tableBorderDxfId="117">
+  <autoFilter ref="B4:I29"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="8"/>
-    <tableColumn id="2" name="CLIENTE" dataDxfId="7"/>
-    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="6"/>
-    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="5"/>
-    <tableColumn id="5" name="STATUS" dataDxfId="4"/>
-    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="3">
-      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
+    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="65"/>
+    <tableColumn id="2" name="CLIENTE" dataDxfId="64"/>
+    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="63"/>
+    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="62"/>
+    <tableColumn id="5" name="STATUS" dataDxfId="61">
+      <calculatedColumnFormula>IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="2"/>
-    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="1"/>
+    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="60"/>
+    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="59"/>
+    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1988,7 +5448,7 @@
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -2007,18 +5467,15 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="F5" s="3" t="str">
         <f ca="1">IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
-        <v>PAGO</v>
-      </c>
-      <c r="G5" s="4">
-        <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G5" s="4"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
@@ -2035,17 +5492,18 @@
       <c r="E6" s="6">
         <v>217311</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>14</v>
+      <c r="F6" s="3" t="str">
+        <f t="shared" ref="F6:F31" ca="1" si="0">IF(G6&lt;&gt;"","PAGO",IF(B6&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
+        <v>PAGO</v>
       </c>
       <c r="G6" s="4">
         <v>46216</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2053,24 +5511,25 @@
         <v>46208</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="E7" s="6">
         <v>452135</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
+      <c r="F7" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G7" s="4">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2078,25 +5537,26 @@
         <v>46217</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="6">
         <v>155331</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>14</v>
+      <c r="F8" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G8" s="4">
         <v>46218</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2104,24 +5564,22 @@
         <v>46171</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6">
         <v>65169</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" ref="G9:G11" ca="1" si="0">TODAY()</f>
-        <v>46222</v>
-      </c>
+      <c r="F9" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G9" s="4"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2129,24 +5587,22 @@
         <v>46234</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" s="6">
         <v>190566</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F10" s="3" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>46222</v>
-      </c>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G10" s="4"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2154,24 +5610,25 @@
         <v>46182</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" s="6">
         <v>269948</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>19</v>
+      <c r="F11" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46222</v>
+        <f t="shared" ref="G9:G11" ca="1" si="1">TODAY()</f>
+        <v>46223</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2179,25 +5636,26 @@
         <v>46240</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6">
         <v>498749</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>14</v>
+      <c r="F12" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G12" s="4">
         <v>46235</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2205,25 +5663,26 @@
         <v>46261</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E13" s="6">
         <v>316793</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>14</v>
+      <c r="F13" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G13" s="4">
         <v>46261</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2231,7 +5690,7 @@
         <v>46173</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>13</v>
@@ -2239,17 +5698,18 @@
       <c r="E14" s="6">
         <v>249298</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>14</v>
+      <c r="F14" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G14" s="4">
         <v>46174</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2257,25 +5717,24 @@
         <v>46212</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="6">
         <v>331687</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46208</v>
-      </c>
+      <c r="F15" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G15" s="4"/>
       <c r="H15" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2283,7 +5742,7 @@
         <v>46192</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>13</v>
@@ -2291,16 +5750,14 @@
       <c r="E16" s="6">
         <v>128638</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" ref="G16:G17" ca="1" si="1">TODAY()</f>
-        <v>46222</v>
-      </c>
+      <c r="F16" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G16" s="4"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -2308,24 +5765,22 @@
         <v>46220</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="6">
         <v>256332</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46222</v>
-      </c>
+      <c r="F17" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G17" s="4"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -2333,25 +5788,26 @@
         <v>46211</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E18" s="6">
         <v>407113</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>14</v>
+      <c r="F18" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G18" s="4">
         <v>46206</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -2359,25 +5815,26 @@
         <v>46202</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E19" s="6">
         <v>474394</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
+      <c r="F19" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G19" s="4">
         <v>46199</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -2385,25 +5842,26 @@
         <v>46232</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="6">
         <v>35608</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>14</v>
+      <c r="F20" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G20" s="4">
         <v>46232</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -2411,25 +5869,26 @@
         <v>46178</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E21" s="6">
         <v>457593</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
+      <c r="F21" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G21" s="4">
         <v>46173</v>
       </c>
       <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -2437,24 +5896,22 @@
         <v>46264</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="6">
         <v>306694</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="4">
-        <f t="shared" ref="G22:G24" ca="1" si="2">TODAY()</f>
-        <v>46222</v>
-      </c>
+      <c r="F22" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -2465,21 +5922,19 @@
         <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" s="6">
         <v>479918</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
-      </c>
+      <c r="F23" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G23" s="4"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -2487,24 +5942,25 @@
         <v>46248</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" s="6">
         <v>357209</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>19</v>
+      <c r="F24" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46222</v>
+        <f t="shared" ref="G22:G24" ca="1" si="2">TODAY()</f>
+        <v>46223</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -2512,25 +5968,26 @@
         <v>46260</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" s="6">
         <v>227667</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>14</v>
+      <c r="F25" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G25" s="4">
         <v>46258</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -2541,22 +5998,23 @@
         <v>12</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="6">
         <v>276131</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>14</v>
+      <c r="F26" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G26" s="4">
         <v>46254</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -2564,25 +6022,26 @@
         <v>46248</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" s="6">
         <v>486368</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>14</v>
+      <c r="F27" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G27" s="4">
         <v>46244</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -2590,24 +6049,25 @@
         <v>46199</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" s="6">
         <v>497059</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>19</v>
+      <c r="F28" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G28" s="4">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -2615,25 +6075,26 @@
         <v>46251</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E29" s="6">
         <v>472564</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>14</v>
+      <c r="F29" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
       </c>
       <c r="G29" s="4">
         <v>46250</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
@@ -2641,24 +6102,22 @@
         <v>46183</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E30" s="6">
         <v>290965</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="4">
-        <f t="shared" ref="G30:G31" ca="1" si="3">TODAY()</f>
-        <v>46222</v>
-      </c>
+      <c r="F30" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G30" s="4"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -2666,35 +6125,33 @@
         <v>46220</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E31" s="6">
         <v>393238</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="4">
-        <f t="shared" ca="1" si="3"/>
-        <v>46222</v>
-      </c>
+      <c r="F31" s="3" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G31" s="4"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F31">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="equal">
       <formula>"PAGO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
       <formula>"PENDENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2714,13 +6171,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
@@ -2731,681 +6188,691 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="E1" s="21"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
-        <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="str">
-        <f ca="1">IF(G4&lt;&gt;"","PAGO",IF(B4&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
-        <v>PAGO</v>
-      </c>
-      <c r="G4" s="13">
-        <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="14">
+      <c r="B5" s="12">
+        <f ca="1">TODAY()</f>
+        <v>46223</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="13" t="str">
+        <f t="shared" ref="F5:F29" ca="1" si="0">IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
+        <v>PAGO</v>
+      </c>
+      <c r="G5" s="14">
+        <f ca="1">TODAY()</f>
+        <v>46223</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="15">
         <v>46281</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="C6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="24">
         <v>99157</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="16">
+      <c r="F6" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G6" s="17">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
-        <v>46257</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1137025</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="16">
-        <v>46255</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="15" t="s">
+        <v>46223</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
+      <c r="B7" s="15">
+        <v>46257</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="24">
+        <v>1137025</v>
+      </c>
+      <c r="F7" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G7" s="17">
+        <v>46255</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15">
         <v>46169</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="C8" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="24">
         <v>1001343</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="F8" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G8" s="17">
         <v>46167</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
-        <v>46273</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="15">
-        <v>374734</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="16">
-        <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15" t="s">
-        <v>33</v>
+      <c r="H8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="14">
+      <c r="B9" s="15">
+        <v>46273</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="24">
+        <v>374734</v>
+      </c>
+      <c r="F9" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G9" s="17">
+        <f ca="1">TODAY()</f>
+        <v>46223</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="15">
         <v>46261</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="C10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="24">
         <v>971237</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F10" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G10" s="17">
+        <v>46257</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="16">
-        <v>46257</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="14">
-        <v>46167</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="15">
-        <v>1282241</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="16">
-        <v>46169</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>40</v>
+      <c r="I10" s="16" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="14">
+      <c r="B11" s="15">
+        <v>46167</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="24">
+        <v>1282241</v>
+      </c>
+      <c r="F11" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G11" s="17">
+        <v>46169</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="15">
         <v>46228</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="C12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="24">
         <v>278593</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="16">
+      <c r="F12" s="16" t="str">
+        <f ca="1">IF(G12&lt;&gt;"","PAGO",IF(B12&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
+        <v>PAGO</v>
+      </c>
+      <c r="G12" s="17">
         <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
-        <v>46278</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="15">
-        <v>1293239</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="16">
-        <v>46279</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>24</v>
+        <v>46223</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
+      <c r="B13" s="15">
+        <v>46278</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="24">
+        <v>1293239</v>
+      </c>
+      <c r="F13" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="15">
         <v>46280</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="C14" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="24">
         <v>12266</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="16">
+      <c r="F14" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G14" s="17">
         <v>46281</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
-        <v>46267</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="15">
-        <v>147901</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="16">
-        <v>46263</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>33</v>
+      <c r="H14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="14">
+      <c r="B15" s="15">
+        <v>46267</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="24">
+        <v>147901</v>
+      </c>
+      <c r="F15" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G15" s="17">
+        <v>46263</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="15">
         <v>46177</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="C16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="24">
         <v>561159</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="16">
-        <v>46177</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="14">
-        <v>46247</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="15">
-        <v>71884</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="16">
-        <v>46249</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>40</v>
+      <c r="F16" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="14">
+      <c r="B17" s="15">
+        <v>46247</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="24">
+        <v>71884</v>
+      </c>
+      <c r="F17" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G17" s="17">
+        <v>46249</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="15">
         <v>46223</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="C18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="24">
         <v>44260</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="16">
+      <c r="F18" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G18" s="17">
         <v>46221</v>
       </c>
-      <c r="H17" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="14">
-        <v>46219</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="15">
-        <v>607481</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="16">
-        <v>46220</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>33</v>
+      <c r="H18" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="14">
+      <c r="B19" s="15">
+        <v>46219</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="24">
+        <v>607481</v>
+      </c>
+      <c r="F19" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G19" s="17">
+        <v>46220</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="15">
         <v>46254</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="C20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="24">
         <v>1337831</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="16">
-        <f ca="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="14">
-        <v>46179</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="15">
-        <v>522722</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="16">
-        <v>46181</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>40</v>
+      <c r="F20" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="14">
+      <c r="B21" s="15">
+        <v>46179</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="24">
+        <v>522722</v>
+      </c>
+      <c r="F21" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G21" s="17">
+        <v>46181</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="15">
         <v>46208</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="C22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="24">
         <v>922892</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="16">
+      <c r="F22" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G22" s="17">
         <v>46207</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="14">
-        <v>46170</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="15">
-        <v>1393655</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="16">
-        <v>46172</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>16</v>
+      <c r="H22" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="14">
+      <c r="B23" s="15">
+        <v>46170</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="24">
+        <v>1393655</v>
+      </c>
+      <c r="F23" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G23" s="17">
+        <v>46172</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="15">
         <v>46275</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="C24" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="24">
         <v>377976</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="16">
-        <f t="shared" ref="G23:G24" ca="1" si="0">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
-        <v>46263</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="15">
-        <v>1468989</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="16">
+      <c r="F24" s="16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>46222</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15" t="s">
-        <v>40</v>
+        <v>PAGO</v>
+      </c>
+      <c r="G24" s="17">
+        <f t="shared" ref="G24:G25" ca="1" si="1">TODAY()</f>
+        <v>46223</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="14">
+      <c r="B25" s="15">
+        <v>46263</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="24">
+        <v>1468989</v>
+      </c>
+      <c r="F25" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G25" s="17">
+        <f t="shared" ca="1" si="1"/>
+        <v>46223</v>
+      </c>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="15">
         <v>46232</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="C26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="24">
         <v>643132</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="16">
+      <c r="F26" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G26" s="17">
         <v>46231</v>
       </c>
-      <c r="H25" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="14">
-        <v>46248</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="15">
-        <v>890403</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="16">
-        <f t="shared" ref="G26:G28" ca="1" si="1">TODAY()</f>
-        <v>46222</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15" t="s">
-        <v>16</v>
+      <c r="H26" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="14">
+      <c r="B27" s="15">
+        <v>46248</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="24">
+        <v>890403</v>
+      </c>
+      <c r="F27" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G27" s="17">
+        <f t="shared" ref="G27:G29" ca="1" si="2">TODAY()</f>
+        <v>46223</v>
+      </c>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="15">
         <v>46185</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="15">
+      <c r="C28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="24">
         <v>159442</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="16">
-        <f t="shared" ca="1" si="1"/>
-        <v>46222</v>
-      </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15" t="s">
-        <v>20</v>
+      <c r="F28" s="16" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G28" s="17"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="15">
         <v>46176</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="E29" s="24">
         <v>955553</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="16">
-        <f t="shared" ca="1" si="1"/>
-        <v>46222</v>
-      </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15" t="s">
-        <v>40</v>
+      <c r="F29" s="13" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G29" s="17"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F28">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:F29">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"PAGO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"PENDENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H29">
       <formula1>"BOLETO,TRANSFERENCIA,PIX,DEBITO,CREDITO,DINHEIRO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3420,17 +6887,297 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" customWidth="1"/>
+    <col min="18" max="18" width="19" customWidth="1"/>
+    <col min="19" max="19" width="21.85546875" customWidth="1"/>
+    <col min="20" max="20" width="19.5703125" customWidth="1"/>
+    <col min="21" max="21" width="22" customWidth="1"/>
+    <col min="22" max="22" width="20.42578125" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" customWidth="1"/>
+    <col min="24" max="24" width="21.5703125" customWidth="1"/>
+    <col min="25" max="25" width="20.28515625" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="27" width="16.5703125" customWidth="1"/>
+    <col min="28" max="28" width="16" customWidth="1"/>
+    <col min="29" max="29" width="20.28515625" customWidth="1"/>
+    <col min="30" max="30" width="18.85546875" customWidth="1"/>
+    <col min="31" max="31" width="20.28515625" customWidth="1"/>
+    <col min="32" max="32" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" customWidth="1"/>
+    <col min="36" max="36" width="11.85546875" customWidth="1"/>
+    <col min="37" max="37" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="23" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.7109375" customWidth="1"/>
+    <col min="53" max="53" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="H4" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="27">
+        <v>249298</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27">
+        <v>65169</v>
+      </c>
+      <c r="F6" s="27">
+        <v>314467</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="19">
+        <v>3677239</v>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19">
+        <v>3677239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="27">
+        <v>1698994</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27">
+        <v>419603</v>
+      </c>
+      <c r="F7" s="27">
+        <v>2118597</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="19">
+        <v>522722</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19">
+        <v>1676154</v>
+      </c>
+      <c r="L7" s="19">
+        <v>2198876</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="27">
+        <v>1267498</v>
+      </c>
+      <c r="D8" s="27">
+        <v>190566</v>
+      </c>
+      <c r="E8" s="27">
+        <v>1461175</v>
+      </c>
+      <c r="F8" s="27">
+        <v>2919239</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="19">
+        <v>2496358</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19">
+        <v>2496358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="27">
+        <v>2635481</v>
+      </c>
+      <c r="D9" s="27">
+        <v>306694</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27">
+        <v>2942175</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="19">
+        <v>4539538</v>
+      </c>
+      <c r="J9" s="19">
+        <v>1337831</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19">
+        <v>5877369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="26">
+        <v>5851271</v>
+      </c>
+      <c r="D10" s="26">
+        <v>497260</v>
+      </c>
+      <c r="E10" s="26">
+        <v>1945947</v>
+      </c>
+      <c r="F10" s="26">
+        <v>8294478</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="19">
+        <v>1012034</v>
+      </c>
+      <c r="J10" s="19">
+        <v>1293239</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19">
+        <v>2305273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="19">
+        <v>12247891</v>
+      </c>
+      <c r="J11" s="19">
+        <v>2631070</v>
+      </c>
+      <c r="K11" s="19">
+        <v>1676154</v>
+      </c>
+      <c r="L11" s="19">
+        <v>16555115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
--- a/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
+++ b/Excel/excel-dashboard-financeiro/Dashboard Financeiro/excel-dashboard-financeiro.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="89">
   <si>
     <t>CONTAS A RECEBER</t>
   </si>
@@ -724,6 +724,175 @@
   </cellStyles>
   <dxfs count="176">
     <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="singleAccounting"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <u val="none"/>
       </font>
@@ -771,569 +940,6 @@
     <dxf>
       <font>
         <u val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="1"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="1"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="1"/>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="bottom" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="14"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="singleAccounting"/>
       </font>
     </dxf>
     <dxf>
@@ -1704,38 +1310,432 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
+        <sz val="12"/>
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <sz val="12"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <sz val="14"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <sz val="14"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <b val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <b val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <sz val="12"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <sz val="12"/>
+      </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="1"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="1"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="1"/>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2579,7 +2579,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-51EE-45B2-AB66-E90385E04409}"/>
+              <c16:uniqueId val="{00000003-51EE-45B2-AB66-E90385E04409}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2653,7 +2653,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51EE-45B2-AB66-E90385E04409}"/>
+              <c16:uniqueId val="{00000004-51EE-45B2-AB66-E90385E04409}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2730,7 +2730,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-51EE-45B2-AB66-E90385E04409}"/>
+              <c16:uniqueId val="{00000005-51EE-45B2-AB66-E90385E04409}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3274,6 +3274,69 @@
               </a:outerShdw>
             </a:effectLst>
           </c:spPr>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:ln w="34925" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
@@ -4713,6 +4776,138 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -5818,7 +6013,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-801F-4251-9D72-14326BD46D2B}"/>
+              <c16:uniqueId val="{00000003-801F-4251-9D72-14326BD46D2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5912,7 +6107,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-801F-4251-9D72-14326BD46D2B}"/>
+              <c16:uniqueId val="{00000004-801F-4251-9D72-14326BD46D2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6009,7 +6204,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-801F-4251-9D72-14326BD46D2B}"/>
+              <c16:uniqueId val="{00000005-801F-4251-9D72-14326BD46D2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12937,25 +13132,25 @@
     <dataField name="TOTAL DE RECEITAS" fld="3" baseField="8" baseItem="5" numFmtId="44"/>
   </dataFields>
   <formats count="55">
-    <format dxfId="147">
+    <format dxfId="0">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="146">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="145">
+    <format dxfId="2">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="144">
+    <format dxfId="3">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="143">
+    <format dxfId="4">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="142">
+    <format dxfId="5">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="141">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="5">
@@ -12968,167 +13163,167 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="140">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="139">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="138">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="137">
+    <format dxfId="10">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="96">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="89">
+    <format dxfId="12">
       <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="13">
       <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="14">
       <pivotArea dataOnly="0" grandRow="1" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="15">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="82">
+    <format dxfId="17">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="81">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="19">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="21">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="70">
+    <format dxfId="23">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="25">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="61">
+    <format dxfId="26">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="27">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="57">
+    <format dxfId="30">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="33">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="51">
+    <format dxfId="36">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="39">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="42">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="45">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="47">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="48">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="49">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="50">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="5">
@@ -13141,17 +13336,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -13690,106 +13885,106 @@
     <dataField name="TOTAL DE DESPESAS" fld="3" baseField="8" baseItem="5" numFmtId="164"/>
   </dataFields>
   <formats count="60">
-    <format dxfId="97">
+    <format dxfId="55">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="98">
+    <format dxfId="56">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="57">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="100">
+    <format dxfId="58">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="101">
+    <format dxfId="59">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="102">
+    <format dxfId="60">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="103">
+    <format dxfId="61">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="104">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="105">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="106">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="107">
+    <format dxfId="65">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="109">
+    <format dxfId="67">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="68">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="111">
+    <format dxfId="69">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="70">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="113">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="114">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="115">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="116">
+    <format dxfId="74">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="117">
+    <format dxfId="75">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="118">
+    <format dxfId="76">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="119">
+    <format dxfId="77">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="120">
+    <format dxfId="78">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="121">
+    <format dxfId="79">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="122">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="123">
+    <format dxfId="81">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="124">
+    <format dxfId="82">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="125">
+    <format dxfId="83">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="126">
+    <format dxfId="84">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -13798,7 +13993,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="127">
+    <format dxfId="85">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -13807,7 +14002,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="128">
+    <format dxfId="86">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -13816,7 +14011,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="129">
+    <format dxfId="87">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -13825,19 +14020,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="130">
+    <format dxfId="88">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="131">
+    <format dxfId="89">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="90">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="91">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="134">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="4">
@@ -13849,78 +14044,78 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="135">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="136">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="95">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="93">
+    <format dxfId="97">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="99">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="90">
+    <format dxfId="100">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="101">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="103">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="104">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="105">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="73">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="72">
+    <format dxfId="107">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="109">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="110">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="111">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="112">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="64">
+    <format dxfId="113">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="114">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -14008,23 +14203,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabela5" displayName="Tabela5" ref="G3:O55" totalsRowShown="0" headerRowDxfId="22" dataDxfId="10" headerRowBorderDxfId="20" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabela5" displayName="Tabela5" ref="G3:O55" totalsRowShown="0" headerRowDxfId="127" dataDxfId="115" headerRowBorderDxfId="125" tableBorderDxfId="126">
   <autoFilter ref="G3:O55"/>
   <sortState ref="G4:O55">
     <sortCondition ref="G8:G60"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="19"/>
-    <tableColumn id="2" name="FORNECEDOR" dataDxfId="18"/>
-    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="17"/>
-    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="16" dataCellStyle="Moeda"/>
-    <tableColumn id="5" name="STATUS" dataDxfId="15">
+    <tableColumn id="1" name="DATA DE VENCIMENTO" dataDxfId="124"/>
+    <tableColumn id="2" name="FORNECEDOR" dataDxfId="123"/>
+    <tableColumn id="3" name="DESCRIÇÃO" dataDxfId="122"/>
+    <tableColumn id="4" name="VALOR A PAGAR" dataDxfId="121" dataCellStyle="Moeda"/>
+    <tableColumn id="5" name="STATUS" dataDxfId="120">
       <calculatedColumnFormula>IF(L4&lt;&gt;"","PAGO",IF(G4&lt;TODAY(),"ATRASADO","PENDENTE"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="14"/>
-    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="13"/>
-    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="12"/>
-    <tableColumn id="9" name="TIPO" dataDxfId="11"/>
+    <tableColumn id="6" name="DATA DE PAGAMENTO" dataDxfId="119"/>
+    <tableColumn id="7" name="TIPO DE PAGAMENTO" dataDxfId="118"/>
+    <tableColumn id="8" name="CENTRO DE CUSTO" dataDxfId="117"/>
+    <tableColumn id="9" name="TIPO" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15931,7 +16126,12 @@
         <v>46225</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6">
+        <v>217311</v>
+      </c>
       <c r="F5" s="3" t="str">
         <f ca="1">IF(G5&lt;&gt;"","PAGO",IF(B5&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
         <v>PENDENTE</v>
@@ -15955,11 +16155,9 @@
       </c>
       <c r="F6" s="3" t="str">
         <f ca="1">IF(G6&lt;&gt;"","PAGO",IF(B6&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
-        <v>PAGO</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46216</v>
-      </c>
+        <v>ATRASADO</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="5" t="s">
         <v>14</v>
       </c>
@@ -16610,13 +16808,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F31">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="1" operator="equal">
       <formula>"PAGO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="2" operator="equal">
       <formula>"PENDENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16717,12 +16915,9 @@
       </c>
       <c r="F6" s="15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>PAGO</v>
-      </c>
-      <c r="G6" s="16">
-        <f ca="1">TODAY()</f>
-        <v>46225</v>
-      </c>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G6" s="16"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15" t="s">
         <v>38</v>
@@ -16877,12 +17072,9 @@
       </c>
       <c r="F12" s="15" t="str">
         <f ca="1">IF(G12&lt;&gt;"","PAGO",IF(B12&lt;TODAY(),"ATRASADO","PENDENTE"))</f>
-        <v>PAGO</v>
-      </c>
-      <c r="G12" s="16">
-        <f ca="1">TODAY()</f>
-        <v>46225</v>
-      </c>
+        <v>PENDENTE</v>
+      </c>
+      <c r="G12" s="16"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
         <v>18</v>
@@ -16982,9 +17174,11 @@
       </c>
       <c r="F16" s="15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ATRASADO</v>
-      </c>
-      <c r="G16" s="16"/>
+        <v>PAGO</v>
+      </c>
+      <c r="G16" s="16">
+        <v>46263</v>
+      </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
         <v>15</v>
@@ -17328,13 +17522,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F29">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="1" operator="equal">
       <formula>"PAGO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="2" operator="equal">
       <formula>"PENDENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="3" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17787,28 +17981,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q7:Q8">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="1" operator="equal">
       <formula>"A RECEBER"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="2" operator="equal">
       <formula>"A PAGAR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="3" operator="equal">
       <formula>"A PAGAR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="4" operator="equal">
       <formula>"A PAGAR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="5" operator="equal">
       <formula>"A PAGAR"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="6" operator="equal">
       <formula>"A RECEBER"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="7" operator="equal">
       <formula>"A RECEBER"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="8" operator="equal">
       <formula>"A PAGAR"</formula>
     </cfRule>
     <cfRule type="containsText" priority="9" operator="containsText" text="A PAGAR">
